--- a/JsonConverter/ExcelFiles/BuyAndSell.xlsx
+++ b/JsonConverter/ExcelFiles/BuyAndSell.xlsx
@@ -46,25 +46,120 @@
     <t xml:space="preserve">Trade_Id</t>
   </si>
   <si>
-    <t xml:space="preserve">Gold_0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuel_0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplies_0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TradingGoods_0007</t>
+    <t xml:space="preserve">Gold_0001_Multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel_0002_Multiplier</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Supplies_0003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Multiplier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0004</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Multiplier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Multiplier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Multiplier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TradingGoods_0007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">_Multiplier</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">BuyAndSell_0001</t>
@@ -273,6 +368,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -283,10 +382,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -589,7 +684,7 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -624,41 +719,41 @@
       </c>
     </row>
     <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
